--- a/data/lm-moorestown-basketball.xlsx
+++ b/data/lm-moorestown-basketball.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\lm-moorestown-basketball\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D858BD-59F1-4FDA-8461-2925B4A961CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A782DF-8C4D-4C7F-889F-F81BFAFEFC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="756" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6059" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6238" uniqueCount="527">
   <si>
     <t>week</t>
   </si>
@@ -1611,6 +1611,48 @@
   </si>
   <si>
     <t>Hakim Jackson</t>
+  </si>
+  <si>
+    <t>Brett Ziller</t>
+  </si>
+  <si>
+    <t>2026-p-qf-01</t>
+  </si>
+  <si>
+    <t>2026-p-qf-02</t>
+  </si>
+  <si>
+    <t>2026-p-qf-g02</t>
+  </si>
+  <si>
+    <t>Patrick Bellino</t>
+  </si>
+  <si>
+    <t>Mike Ziller</t>
+  </si>
+  <si>
+    <t>Angel Carrion</t>
+  </si>
+  <si>
+    <t>Thomas Nasto</t>
+  </si>
+  <si>
+    <t>Gates Brooks</t>
+  </si>
+  <si>
+    <t>Manthan Tailor</t>
+  </si>
+  <si>
+    <t>Janos Vajda</t>
+  </si>
+  <si>
+    <t>Connor Stine</t>
+  </si>
+  <si>
+    <t>Allen Harley</t>
+  </si>
+  <si>
+    <t>Ricky Riaz</t>
   </si>
 </sst>
 </file>
@@ -1622,7 +1664,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1644,6 +1686,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1664,7 +1712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1734,11 +1782,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1775,6 +1832,13 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5392,7 +5456,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr defaultColWidth="24.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -7812,8 +7876,109 @@
         <v>311</v>
       </c>
     </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>514</v>
+      </c>
+      <c r="B42">
+        <v>2026</v>
+      </c>
+      <c r="C42" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46175</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42">
+        <v>60</v>
+      </c>
+      <c r="O42">
+        <v>20</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>18</v>
+      </c>
+      <c r="R42" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>515</v>
+      </c>
+      <c r="B43">
+        <v>2026</v>
+      </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46175</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43">
+        <v>31</v>
+      </c>
+      <c r="K43">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>16</v>
+      </c>
+      <c r="M43">
+        <v>23</v>
+      </c>
+      <c r="N43">
+        <v>47</v>
+      </c>
+      <c r="O43">
+        <v>47</v>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>18</v>
+      </c>
+      <c r="R43" t="s">
+        <v>311</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T41" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -7856,8 +8021,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614AF34C-B63C-4CF6-8513-43F58983B75E}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U506"/>
+  <dimension ref="A1:U521"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -7941,7 +8105,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>353</v>
       </c>
@@ -8009,7 +8173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>353</v>
       </c>
@@ -8077,7 +8241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>353</v>
       </c>
@@ -8145,7 +8309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>353</v>
       </c>
@@ -8213,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>353</v>
       </c>
@@ -8281,7 +8445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>353</v>
       </c>
@@ -8349,7 +8513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>353</v>
       </c>
@@ -8417,7 +8581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>353</v>
       </c>
@@ -8485,7 +8649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>353</v>
       </c>
@@ -8553,7 +8717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>353</v>
       </c>
@@ -8621,7 +8785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>353</v>
       </c>
@@ -8689,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>353</v>
       </c>
@@ -8757,7 +8921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>353</v>
       </c>
@@ -8825,7 +8989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>353</v>
       </c>
@@ -8893,7 +9057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>353</v>
       </c>
@@ -8961,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>353</v>
       </c>
@@ -9029,7 +9193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>352</v>
       </c>
@@ -9097,7 +9261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>352</v>
       </c>
@@ -9165,7 +9329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>352</v>
       </c>
@@ -9233,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>352</v>
       </c>
@@ -9301,7 +9465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>352</v>
       </c>
@@ -9369,7 +9533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>352</v>
       </c>
@@ -9437,7 +9601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>352</v>
       </c>
@@ -9505,7 +9669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>352</v>
       </c>
@@ -9573,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>352</v>
       </c>
@@ -9641,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>352</v>
       </c>
@@ -9709,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>352</v>
       </c>
@@ -9777,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>352</v>
       </c>
@@ -9845,7 +10009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>352</v>
       </c>
@@ -9913,7 +10077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>352</v>
       </c>
@@ -9981,7 +10145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>352</v>
       </c>
@@ -10049,7 +10213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>352</v>
       </c>
@@ -10117,7 +10281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>351</v>
       </c>
@@ -10185,7 +10349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>351</v>
       </c>
@@ -10253,7 +10417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>351</v>
       </c>
@@ -10321,7 +10485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>351</v>
       </c>
@@ -10389,7 +10553,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>351</v>
       </c>
@@ -10457,7 +10621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>351</v>
       </c>
@@ -10525,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>351</v>
       </c>
@@ -10593,7 +10757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>351</v>
       </c>
@@ -10661,7 +10825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>351</v>
       </c>
@@ -10729,7 +10893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>351</v>
       </c>
@@ -10797,7 +10961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>351</v>
       </c>
@@ -10865,7 +11029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>351</v>
       </c>
@@ -10933,7 +11097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>351</v>
       </c>
@@ -11001,7 +11165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>350</v>
       </c>
@@ -11069,7 +11233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>350</v>
       </c>
@@ -11137,7 +11301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>350</v>
       </c>
@@ -11205,7 +11369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>350</v>
       </c>
@@ -11273,7 +11437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>350</v>
       </c>
@@ -11341,7 +11505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
         <v>350</v>
       </c>
@@ -11409,7 +11573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>350</v>
       </c>
@@ -11477,7 +11641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>350</v>
       </c>
@@ -11545,7 +11709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>350</v>
       </c>
@@ -11613,7 +11777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>350</v>
       </c>
@@ -11681,7 +11845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>350</v>
       </c>
@@ -11749,7 +11913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>350</v>
       </c>
@@ -11817,7 +11981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>350</v>
       </c>
@@ -11885,7 +12049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
         <v>350</v>
       </c>
@@ -11953,7 +12117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>349</v>
       </c>
@@ -12021,7 +12185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>349</v>
       </c>
@@ -12089,7 +12253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>349</v>
       </c>
@@ -12157,7 +12321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
         <v>349</v>
       </c>
@@ -12225,7 +12389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>349</v>
       </c>
@@ -12293,7 +12457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
         <v>349</v>
       </c>
@@ -12361,7 +12525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>349</v>
       </c>
@@ -12429,7 +12593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>349</v>
       </c>
@@ -12497,7 +12661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
         <v>349</v>
       </c>
@@ -12565,7 +12729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
         <v>349</v>
       </c>
@@ -12633,7 +12797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
         <v>349</v>
       </c>
@@ -12701,7 +12865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
         <v>349</v>
       </c>
@@ -12769,7 +12933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
         <v>349</v>
       </c>
@@ -12837,7 +13001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
         <v>349</v>
       </c>
@@ -12905,7 +13069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>349</v>
       </c>
@@ -12973,7 +13137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
         <v>349</v>
       </c>
@@ -13041,7 +13205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
         <v>348</v>
       </c>
@@ -13109,7 +13273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
         <v>348</v>
       </c>
@@ -13177,7 +13341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>348</v>
       </c>
@@ -13245,7 +13409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>348</v>
       </c>
@@ -13313,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>348</v>
       </c>
@@ -13381,7 +13545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
         <v>348</v>
       </c>
@@ -13449,7 +13613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>348</v>
       </c>
@@ -13517,7 +13681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
         <v>348</v>
       </c>
@@ -13585,7 +13749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
         <v>348</v>
       </c>
@@ -13653,7 +13817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
         <v>348</v>
       </c>
@@ -13721,7 +13885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="14" t="s">
         <v>348</v>
       </c>
@@ -13789,7 +13953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
         <v>348</v>
       </c>
@@ -13857,7 +14021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>348</v>
       </c>
@@ -13925,7 +14089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
         <v>348</v>
       </c>
@@ -13993,7 +14157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>348</v>
       </c>
@@ -14061,7 +14225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
         <v>347</v>
       </c>
@@ -14129,7 +14293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
         <v>347</v>
       </c>
@@ -14197,7 +14361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
         <v>347</v>
       </c>
@@ -14265,7 +14429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
         <v>347</v>
       </c>
@@ -14333,7 +14497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
         <v>347</v>
       </c>
@@ -14401,7 +14565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
         <v>347</v>
       </c>
@@ -14469,7 +14633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
         <v>347</v>
       </c>
@@ -14537,7 +14701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
         <v>347</v>
       </c>
@@ -14605,7 +14769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
         <v>347</v>
       </c>
@@ -14673,7 +14837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
         <v>347</v>
       </c>
@@ -14741,7 +14905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>347</v>
       </c>
@@ -14809,7 +14973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
         <v>347</v>
       </c>
@@ -14877,7 +15041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
         <v>347</v>
       </c>
@@ -14945,7 +15109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
         <v>347</v>
       </c>
@@ -15013,7 +15177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
         <v>347</v>
       </c>
@@ -15081,7 +15245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
         <v>346</v>
       </c>
@@ -15149,7 +15313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
         <v>346</v>
       </c>
@@ -15217,7 +15381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
         <v>346</v>
       </c>
@@ -15285,7 +15449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
         <v>346</v>
       </c>
@@ -15353,7 +15517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
         <v>346</v>
       </c>
@@ -15421,7 +15585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
         <v>346</v>
       </c>
@@ -15489,7 +15653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
         <v>346</v>
       </c>
@@ -15557,7 +15721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
         <v>346</v>
       </c>
@@ -15625,7 +15789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
         <v>346</v>
       </c>
@@ -15693,7 +15857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
         <v>346</v>
       </c>
@@ -15761,7 +15925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
         <v>346</v>
       </c>
@@ -15829,7 +15993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
         <v>346</v>
       </c>
@@ -15897,7 +16061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
         <v>346</v>
       </c>
@@ -15965,7 +16129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
         <v>346</v>
       </c>
@@ -16033,7 +16197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
         <v>345</v>
       </c>
@@ -16101,7 +16265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
         <v>345</v>
       </c>
@@ -16169,7 +16333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
         <v>345</v>
       </c>
@@ -16237,7 +16401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
         <v>345</v>
       </c>
@@ -16305,7 +16469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
         <v>345</v>
       </c>
@@ -16373,7 +16537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
         <v>345</v>
       </c>
@@ -16441,7 +16605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>345</v>
       </c>
@@ -16509,7 +16673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>345</v>
       </c>
@@ -16577,7 +16741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
         <v>345</v>
       </c>
@@ -16645,7 +16809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
         <v>345</v>
       </c>
@@ -16713,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
         <v>345</v>
       </c>
@@ -16781,7 +16945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="19" t="s">
         <v>345</v>
       </c>
@@ -16849,7 +17013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
         <v>345</v>
       </c>
@@ -16917,7 +17081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="19" t="s">
         <v>345</v>
       </c>
@@ -16985,7 +17149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
         <v>345</v>
       </c>
@@ -17053,7 +17217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
         <v>345</v>
       </c>
@@ -17121,7 +17285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
         <v>344</v>
       </c>
@@ -17189,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>344</v>
       </c>
@@ -17257,7 +17421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="14" t="s">
         <v>344</v>
       </c>
@@ -17325,7 +17489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="19" t="s">
         <v>344</v>
       </c>
@@ -17393,7 +17557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="14" t="s">
         <v>344</v>
       </c>
@@ -17461,7 +17625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
         <v>344</v>
       </c>
@@ -17529,7 +17693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="14" t="s">
         <v>344</v>
       </c>
@@ -17597,7 +17761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
         <v>344</v>
       </c>
@@ -17665,7 +17829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="14" t="s">
         <v>344</v>
       </c>
@@ -17733,7 +17897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
         <v>344</v>
       </c>
@@ -17801,7 +17965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
         <v>344</v>
       </c>
@@ -17869,7 +18033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>344</v>
       </c>
@@ -17937,7 +18101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="14" t="s">
         <v>344</v>
       </c>
@@ -18005,7 +18169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="19" t="s">
         <v>343</v>
       </c>
@@ -18073,7 +18237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
         <v>343</v>
       </c>
@@ -18141,7 +18305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="19" t="s">
         <v>343</v>
       </c>
@@ -18209,7 +18373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="14" t="s">
         <v>343</v>
       </c>
@@ -18277,7 +18441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="19" t="s">
         <v>343</v>
       </c>
@@ -18345,7 +18509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="14" t="s">
         <v>343</v>
       </c>
@@ -18413,7 +18577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="19" t="s">
         <v>343</v>
       </c>
@@ -18481,7 +18645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="14" t="s">
         <v>343</v>
       </c>
@@ -18549,7 +18713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="19" t="s">
         <v>343</v>
       </c>
@@ -18617,7 +18781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
         <v>343</v>
       </c>
@@ -18685,7 +18849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="19" t="s">
         <v>343</v>
       </c>
@@ -18753,7 +18917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>343</v>
       </c>
@@ -18821,7 +18985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="19" t="s">
         <v>343</v>
       </c>
@@ -18889,7 +19053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
         <v>343</v>
       </c>
@@ -18957,7 +19121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="19" t="s">
         <v>343</v>
       </c>
@@ -19025,7 +19189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="14" t="s">
         <v>343</v>
       </c>
@@ -19093,7 +19257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="19" t="s">
         <v>342</v>
       </c>
@@ -19161,7 +19325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="14" t="s">
         <v>342</v>
       </c>
@@ -19229,7 +19393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="19" t="s">
         <v>342</v>
       </c>
@@ -19297,7 +19461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="14" t="s">
         <v>342</v>
       </c>
@@ -19365,7 +19529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="19" t="s">
         <v>342</v>
       </c>
@@ -19433,7 +19597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="14" t="s">
         <v>342</v>
       </c>
@@ -19501,7 +19665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="19" t="s">
         <v>342</v>
       </c>
@@ -19569,7 +19733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="14" t="s">
         <v>342</v>
       </c>
@@ -19637,7 +19801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="19" t="s">
         <v>342</v>
       </c>
@@ -19705,7 +19869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="14" t="s">
         <v>342</v>
       </c>
@@ -19773,7 +19937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="19" t="s">
         <v>342</v>
       </c>
@@ -19841,7 +20005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="14" t="s">
         <v>342</v>
       </c>
@@ -19909,7 +20073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="19" t="s">
         <v>342</v>
       </c>
@@ -19977,7 +20141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="14" t="s">
         <v>342</v>
       </c>
@@ -20045,7 +20209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="19" t="s">
         <v>341</v>
       </c>
@@ -20113,7 +20277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="14" t="s">
         <v>341</v>
       </c>
@@ -20181,7 +20345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="19" t="s">
         <v>341</v>
       </c>
@@ -20249,7 +20413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="14" t="s">
         <v>341</v>
       </c>
@@ -20317,7 +20481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="19" t="s">
         <v>341</v>
       </c>
@@ -20385,7 +20549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="14" t="s">
         <v>341</v>
       </c>
@@ -20453,7 +20617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="19" t="s">
         <v>341</v>
       </c>
@@ -20521,7 +20685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="14" t="s">
         <v>341</v>
       </c>
@@ -20589,7 +20753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="19" t="s">
         <v>341</v>
       </c>
@@ -20657,7 +20821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="14" t="s">
         <v>341</v>
       </c>
@@ -20725,7 +20889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="19" t="s">
         <v>341</v>
       </c>
@@ -20793,7 +20957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="14" t="s">
         <v>341</v>
       </c>
@@ -20861,7 +21025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="19" t="s">
         <v>341</v>
       </c>
@@ -20929,7 +21093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="14" t="s">
         <v>340</v>
       </c>
@@ -20997,7 +21161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="19" t="s">
         <v>340</v>
       </c>
@@ -21065,7 +21229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="14" t="s">
         <v>340</v>
       </c>
@@ -21133,7 +21297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="19" t="s">
         <v>340</v>
       </c>
@@ -21201,7 +21365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="14" t="s">
         <v>340</v>
       </c>
@@ -21269,7 +21433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="19" t="s">
         <v>340</v>
       </c>
@@ -21337,7 +21501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="14" t="s">
         <v>340</v>
       </c>
@@ -21405,7 +21569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="19" t="s">
         <v>340</v>
       </c>
@@ -21473,7 +21637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="14" t="s">
         <v>340</v>
       </c>
@@ -21541,7 +21705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="19" t="s">
         <v>340</v>
       </c>
@@ -21609,7 +21773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="14" t="s">
         <v>340</v>
       </c>
@@ -21677,7 +21841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="19" t="s">
         <v>339</v>
       </c>
@@ -21745,7 +21909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="14" t="s">
         <v>339</v>
       </c>
@@ -21813,7 +21977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="19" t="s">
         <v>339</v>
       </c>
@@ -21881,7 +22045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="14" t="s">
         <v>339</v>
       </c>
@@ -21949,7 +22113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="19" t="s">
         <v>339</v>
       </c>
@@ -22017,7 +22181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="14" t="s">
         <v>339</v>
       </c>
@@ -22085,7 +22249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="19" t="s">
         <v>339</v>
       </c>
@@ -22153,7 +22317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="14" t="s">
         <v>339</v>
       </c>
@@ -22221,7 +22385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="19" t="s">
         <v>339</v>
       </c>
@@ -22289,7 +22453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="14" t="s">
         <v>339</v>
       </c>
@@ -22357,7 +22521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="19" t="s">
         <v>339</v>
       </c>
@@ -22425,7 +22589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="14" t="s">
         <v>339</v>
       </c>
@@ -22493,7 +22657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="19" t="s">
         <v>338</v>
       </c>
@@ -22561,7 +22725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="14" t="s">
         <v>338</v>
       </c>
@@ -22629,7 +22793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="19" t="s">
         <v>338</v>
       </c>
@@ -22697,7 +22861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="14" t="s">
         <v>338</v>
       </c>
@@ -22765,7 +22929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="19" t="s">
         <v>338</v>
       </c>
@@ -22833,7 +22997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="14" t="s">
         <v>338</v>
       </c>
@@ -22901,7 +23065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="19" t="s">
         <v>338</v>
       </c>
@@ -22969,7 +23133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="14" t="s">
         <v>338</v>
       </c>
@@ -23037,7 +23201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="19" t="s">
         <v>338</v>
       </c>
@@ -23105,7 +23269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="14" t="s">
         <v>338</v>
       </c>
@@ -23173,7 +23337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="19" t="s">
         <v>338</v>
       </c>
@@ -23241,7 +23405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="14" t="s">
         <v>338</v>
       </c>
@@ -23309,7 +23473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="19" t="s">
         <v>338</v>
       </c>
@@ -23377,7 +23541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="14" t="s">
         <v>338</v>
       </c>
@@ -23445,7 +23609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="19" t="s">
         <v>338</v>
       </c>
@@ -23513,7 +23677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="14" t="s">
         <v>337</v>
       </c>
@@ -23581,7 +23745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="19" t="s">
         <v>337</v>
       </c>
@@ -23649,7 +23813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="14" t="s">
         <v>337</v>
       </c>
@@ -23717,7 +23881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="19" t="s">
         <v>337</v>
       </c>
@@ -23785,7 +23949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="14" t="s">
         <v>337</v>
       </c>
@@ -23853,7 +24017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="19" t="s">
         <v>337</v>
       </c>
@@ -23921,7 +24085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="14" t="s">
         <v>337</v>
       </c>
@@ -23989,7 +24153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="19" t="s">
         <v>337</v>
       </c>
@@ -24057,7 +24221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="14" t="s">
         <v>337</v>
       </c>
@@ -24125,7 +24289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="19" t="s">
         <v>337</v>
       </c>
@@ -24193,7 +24357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A241" s="14" t="s">
         <v>337</v>
       </c>
@@ -24261,7 +24425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A242" s="19" t="s">
         <v>336</v>
       </c>
@@ -24329,7 +24493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A243" s="14" t="s">
         <v>336</v>
       </c>
@@ -24397,7 +24561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A244" s="19" t="s">
         <v>336</v>
       </c>
@@ -24465,7 +24629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A245" s="14" t="s">
         <v>336</v>
       </c>
@@ -24533,7 +24697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A246" s="19" t="s">
         <v>336</v>
       </c>
@@ -24601,7 +24765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A247" s="14" t="s">
         <v>336</v>
       </c>
@@ -24669,7 +24833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A248" s="19" t="s">
         <v>336</v>
       </c>
@@ -24737,7 +24901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A249" s="14" t="s">
         <v>336</v>
       </c>
@@ -24805,7 +24969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A250" s="19" t="s">
         <v>336</v>
       </c>
@@ -24873,7 +25037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A251" s="14" t="s">
         <v>336</v>
       </c>
@@ -24941,7 +25105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A252" s="19" t="s">
         <v>336</v>
       </c>
@@ -25009,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A253" s="14" t="s">
         <v>336</v>
       </c>
@@ -25077,7 +25241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A254" s="19" t="s">
         <v>335</v>
       </c>
@@ -25145,7 +25309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A255" s="14" t="s">
         <v>335</v>
       </c>
@@ -25213,7 +25377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A256" s="19" t="s">
         <v>335</v>
       </c>
@@ -25281,7 +25445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A257" s="14" t="s">
         <v>335</v>
       </c>
@@ -25349,7 +25513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A258" s="19" t="s">
         <v>335</v>
       </c>
@@ -25417,7 +25581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A259" s="14" t="s">
         <v>335</v>
       </c>
@@ -25485,7 +25649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A260" s="19" t="s">
         <v>335</v>
       </c>
@@ -25553,7 +25717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A261" s="14" t="s">
         <v>335</v>
       </c>
@@ -25621,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A262" s="19" t="s">
         <v>335</v>
       </c>
@@ -25689,7 +25853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A263" s="14" t="s">
         <v>335</v>
       </c>
@@ -25757,7 +25921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A264" s="19" t="s">
         <v>335</v>
       </c>
@@ -25825,7 +25989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A265" s="14" t="s">
         <v>335</v>
       </c>
@@ -25893,7 +26057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A266" s="19" t="s">
         <v>335</v>
       </c>
@@ -25961,7 +26125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A267" s="14" t="s">
         <v>334</v>
       </c>
@@ -26029,7 +26193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A268" s="19" t="s">
         <v>334</v>
       </c>
@@ -26097,7 +26261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A269" s="14" t="s">
         <v>334</v>
       </c>
@@ -26165,7 +26329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A270" s="19" t="s">
         <v>334</v>
       </c>
@@ -26233,7 +26397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A271" s="14" t="s">
         <v>334</v>
       </c>
@@ -26301,7 +26465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A272" s="19" t="s">
         <v>334</v>
       </c>
@@ -26369,7 +26533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A273" s="14" t="s">
         <v>334</v>
       </c>
@@ -26437,7 +26601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A274" s="19" t="s">
         <v>334</v>
       </c>
@@ -26505,7 +26669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A275" s="14" t="s">
         <v>334</v>
       </c>
@@ -26573,7 +26737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A276" s="19" t="s">
         <v>334</v>
       </c>
@@ -26641,7 +26805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A277" s="14" t="s">
         <v>334</v>
       </c>
@@ -26709,7 +26873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A278" s="19" t="s">
         <v>334</v>
       </c>
@@ -26777,7 +26941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A279" s="14" t="s">
         <v>334</v>
       </c>
@@ -26845,7 +27009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A280" s="19" t="s">
         <v>334</v>
       </c>
@@ -26913,7 +27077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A281" s="14" t="s">
         <v>333</v>
       </c>
@@ -26981,7 +27145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A282" s="19" t="s">
         <v>333</v>
       </c>
@@ -27049,7 +27213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A283" s="14" t="s">
         <v>333</v>
       </c>
@@ -27117,7 +27281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A284" s="19" t="s">
         <v>333</v>
       </c>
@@ -27185,7 +27349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A285" s="14" t="s">
         <v>333</v>
       </c>
@@ -27253,7 +27417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A286" s="19" t="s">
         <v>333</v>
       </c>
@@ -27321,7 +27485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A287" s="14" t="s">
         <v>333</v>
       </c>
@@ -27389,7 +27553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A288" s="19" t="s">
         <v>333</v>
       </c>
@@ -27457,7 +27621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A289" s="14" t="s">
         <v>333</v>
       </c>
@@ -27525,7 +27689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A290" s="19" t="s">
         <v>333</v>
       </c>
@@ -27593,7 +27757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A291" s="14" t="s">
         <v>333</v>
       </c>
@@ -27661,7 +27825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A292" s="19" t="s">
         <v>333</v>
       </c>
@@ -27729,7 +27893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A293" s="14" t="s">
         <v>333</v>
       </c>
@@ -27797,7 +27961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A294" s="19" t="s">
         <v>333</v>
       </c>
@@ -27865,7 +28029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A295" s="14" t="s">
         <v>333</v>
       </c>
@@ -27933,7 +28097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A296" s="19" t="s">
         <v>333</v>
       </c>
@@ -28001,7 +28165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A297" s="14" t="s">
         <v>332</v>
       </c>
@@ -28069,7 +28233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A298" s="19" t="s">
         <v>332</v>
       </c>
@@ -28137,7 +28301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A299" s="14" t="s">
         <v>332</v>
       </c>
@@ -28205,7 +28369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A300" s="19" t="s">
         <v>332</v>
       </c>
@@ -28273,7 +28437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A301" s="14" t="s">
         <v>332</v>
       </c>
@@ -28341,7 +28505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A302" s="19" t="s">
         <v>332</v>
       </c>
@@ -28409,7 +28573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A303" s="14" t="s">
         <v>332</v>
       </c>
@@ -28477,7 +28641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A304" s="19" t="s">
         <v>332</v>
       </c>
@@ -28545,7 +28709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A305" s="14" t="s">
         <v>332</v>
       </c>
@@ -28613,7 +28777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A306" s="19" t="s">
         <v>332</v>
       </c>
@@ -28681,7 +28845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A307" s="14" t="s">
         <v>332</v>
       </c>
@@ -28749,7 +28913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A308" s="19" t="s">
         <v>332</v>
       </c>
@@ -28817,7 +28981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A309" s="14" t="s">
         <v>332</v>
       </c>
@@ -28885,7 +29049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A310" s="19" t="s">
         <v>331</v>
       </c>
@@ -28953,7 +29117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A311" s="14" t="s">
         <v>331</v>
       </c>
@@ -29021,7 +29185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A312" s="19" t="s">
         <v>331</v>
       </c>
@@ -29089,7 +29253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A313" s="14" t="s">
         <v>331</v>
       </c>
@@ -29157,7 +29321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A314" s="19" t="s">
         <v>331</v>
       </c>
@@ -29225,7 +29389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A315" s="14" t="s">
         <v>331</v>
       </c>
@@ -29293,7 +29457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A316" s="19" t="s">
         <v>331</v>
       </c>
@@ -29361,7 +29525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A317" s="14" t="s">
         <v>331</v>
       </c>
@@ -29429,7 +29593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A318" s="19" t="s">
         <v>331</v>
       </c>
@@ -29497,7 +29661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A319" s="14" t="s">
         <v>331</v>
       </c>
@@ -29565,7 +29729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A320" s="19" t="s">
         <v>331</v>
       </c>
@@ -29633,7 +29797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A321" s="14" t="s">
         <v>330</v>
       </c>
@@ -29701,7 +29865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A322" s="19" t="s">
         <v>330</v>
       </c>
@@ -29769,7 +29933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A323" s="14" t="s">
         <v>330</v>
       </c>
@@ -29837,7 +30001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A324" s="19" t="s">
         <v>330</v>
       </c>
@@ -29905,7 +30069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A325" s="14" t="s">
         <v>330</v>
       </c>
@@ -29973,7 +30137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A326" s="19" t="s">
         <v>330</v>
       </c>
@@ -30041,7 +30205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A327" s="14" t="s">
         <v>330</v>
       </c>
@@ -30109,7 +30273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A328" s="19" t="s">
         <v>330</v>
       </c>
@@ -30177,7 +30341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A329" s="14" t="s">
         <v>330</v>
       </c>
@@ -30245,7 +30409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A330" s="19" t="s">
         <v>330</v>
       </c>
@@ -30313,7 +30477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A331" s="14" t="s">
         <v>329</v>
       </c>
@@ -30381,7 +30545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A332" s="19" t="s">
         <v>329</v>
       </c>
@@ -30449,7 +30613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A333" s="14" t="s">
         <v>329</v>
       </c>
@@ -30517,7 +30681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A334" s="19" t="s">
         <v>329</v>
       </c>
@@ -30585,7 +30749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A335" s="14" t="s">
         <v>329</v>
       </c>
@@ -30653,7 +30817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A336" s="19" t="s">
         <v>329</v>
       </c>
@@ -30721,7 +30885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A337" s="14" t="s">
         <v>329</v>
       </c>
@@ -30789,7 +30953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A338" s="19" t="s">
         <v>329</v>
       </c>
@@ -30857,7 +31021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A339" s="14" t="s">
         <v>329</v>
       </c>
@@ -30925,7 +31089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A340" s="19" t="s">
         <v>329</v>
       </c>
@@ -30993,7 +31157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A341" s="14" t="s">
         <v>329</v>
       </c>
@@ -31061,7 +31225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A342" s="19" t="s">
         <v>329</v>
       </c>
@@ -31129,7 +31293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A343" s="14" t="s">
         <v>328</v>
       </c>
@@ -31197,7 +31361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A344" s="19" t="s">
         <v>328</v>
       </c>
@@ -31265,7 +31429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A345" s="14" t="s">
         <v>328</v>
       </c>
@@ -31333,7 +31497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A346" s="19" t="s">
         <v>328</v>
       </c>
@@ -31401,7 +31565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A347" s="14" t="s">
         <v>328</v>
       </c>
@@ -31469,7 +31633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A348" s="19" t="s">
         <v>328</v>
       </c>
@@ -31537,7 +31701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A349" s="14" t="s">
         <v>328</v>
       </c>
@@ -31605,7 +31769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A350" s="19" t="s">
         <v>328</v>
       </c>
@@ -31673,7 +31837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A351" s="14" t="s">
         <v>328</v>
       </c>
@@ -31741,7 +31905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A352" s="19" t="s">
         <v>328</v>
       </c>
@@ -31809,7 +31973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A353" s="14" t="s">
         <v>328</v>
       </c>
@@ -31877,7 +32041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A354" s="19" t="s">
         <v>328</v>
       </c>
@@ -31945,7 +32109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A355" s="14" t="s">
         <v>328</v>
       </c>
@@ -32013,7 +32177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A356" s="19" t="s">
         <v>328</v>
       </c>
@@ -32081,7 +32245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A357" s="14" t="s">
         <v>328</v>
       </c>
@@ -32149,7 +32313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A358" s="19" t="s">
         <v>327</v>
       </c>
@@ -32217,7 +32381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A359" s="14" t="s">
         <v>327</v>
       </c>
@@ -32285,7 +32449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A360" s="19" t="s">
         <v>327</v>
       </c>
@@ -32353,7 +32517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="361" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A361" s="14" t="s">
         <v>327</v>
       </c>
@@ -32421,7 +32585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A362" s="19" t="s">
         <v>327</v>
       </c>
@@ -32489,7 +32653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A363" s="14" t="s">
         <v>327</v>
       </c>
@@ -32557,7 +32721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A364" s="19" t="s">
         <v>327</v>
       </c>
@@ -32625,7 +32789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A365" s="14" t="s">
         <v>327</v>
       </c>
@@ -32693,7 +32857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A366" s="19" t="s">
         <v>327</v>
       </c>
@@ -32761,7 +32925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A367" s="14" t="s">
         <v>327</v>
       </c>
@@ -32829,7 +32993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A368" s="19" t="s">
         <v>326</v>
       </c>
@@ -32897,7 +33061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A369" s="14" t="s">
         <v>326</v>
       </c>
@@ -32965,7 +33129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A370" s="19" t="s">
         <v>326</v>
       </c>
@@ -33033,7 +33197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A371" s="14" t="s">
         <v>326</v>
       </c>
@@ -33101,7 +33265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A372" s="19" t="s">
         <v>326</v>
       </c>
@@ -33169,7 +33333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A373" s="14" t="s">
         <v>326</v>
       </c>
@@ -33237,7 +33401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A374" s="19" t="s">
         <v>326</v>
       </c>
@@ -33305,7 +33469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A375" s="14" t="s">
         <v>326</v>
       </c>
@@ -33373,7 +33537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A376" s="19" t="s">
         <v>326</v>
       </c>
@@ -33441,7 +33605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A377" s="14" t="s">
         <v>326</v>
       </c>
@@ -33509,7 +33673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A378" s="19" t="s">
         <v>326</v>
       </c>
@@ -33577,7 +33741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A379" s="14" t="s">
         <v>325</v>
       </c>
@@ -33645,7 +33809,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A380" s="19" t="s">
         <v>325</v>
       </c>
@@ -33713,7 +33877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A381" s="14" t="s">
         <v>325</v>
       </c>
@@ -33781,7 +33945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A382" s="19" t="s">
         <v>325</v>
       </c>
@@ -33849,7 +34013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A383" s="14" t="s">
         <v>325</v>
       </c>
@@ -33917,7 +34081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A384" s="14" t="s">
         <v>325</v>
       </c>
@@ -33985,7 +34149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A385" s="19" t="s">
         <v>325</v>
       </c>
@@ -34053,7 +34217,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A386" s="14" t="s">
         <v>325</v>
       </c>
@@ -34121,7 +34285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A387" s="14" t="s">
         <v>325</v>
       </c>
@@ -34189,7 +34353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A388" s="19" t="s">
         <v>325</v>
       </c>
@@ -34257,7 +34421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A389" s="14" t="s">
         <v>325</v>
       </c>
@@ -34325,7 +34489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A390" s="19" t="s">
         <v>325</v>
       </c>
@@ -34393,7 +34557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A391" s="14" t="s">
         <v>325</v>
       </c>
@@ -34461,7 +34625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A392" s="14" t="s">
         <v>324</v>
       </c>
@@ -34529,7 +34693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A393" s="19" t="s">
         <v>324</v>
       </c>
@@ -34597,7 +34761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A394" s="14" t="s">
         <v>324</v>
       </c>
@@ -34665,7 +34829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A395" s="19" t="s">
         <v>324</v>
       </c>
@@ -34733,7 +34897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A396" s="14" t="s">
         <v>324</v>
       </c>
@@ -34801,7 +34965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A397" s="19" t="s">
         <v>324</v>
       </c>
@@ -34869,7 +35033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A398" s="14" t="s">
         <v>324</v>
       </c>
@@ -34937,7 +35101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A399" s="19" t="s">
         <v>324</v>
       </c>
@@ -35005,7 +35169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A400" s="14" t="s">
         <v>324</v>
       </c>
@@ -35073,7 +35237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A401" s="14" t="s">
         <v>324</v>
       </c>
@@ -35141,7 +35305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A402" s="19" t="s">
         <v>324</v>
       </c>
@@ -35209,7 +35373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A403" s="14" t="s">
         <v>324</v>
       </c>
@@ -35277,7 +35441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A404" s="19" t="s">
         <v>324</v>
       </c>
@@ -35345,7 +35509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A405" s="14" t="s">
         <v>324</v>
       </c>
@@ -35413,7 +35577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A406" s="19" t="s">
         <v>324</v>
       </c>
@@ -35481,7 +35645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A407" s="19" t="s">
         <v>323</v>
       </c>
@@ -35549,7 +35713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A408" s="19" t="s">
         <v>323</v>
       </c>
@@ -35617,7 +35781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A409" s="14" t="s">
         <v>323</v>
       </c>
@@ -35685,7 +35849,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A410" s="14" t="s">
         <v>323</v>
       </c>
@@ -35753,7 +35917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A411" s="19" t="s">
         <v>323</v>
       </c>
@@ -35821,7 +35985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A412" s="14" t="s">
         <v>323</v>
       </c>
@@ -35889,7 +36053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A413" s="19" t="s">
         <v>323</v>
       </c>
@@ -35957,7 +36121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A414" s="14" t="s">
         <v>323</v>
       </c>
@@ -36025,7 +36189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A415" s="19" t="s">
         <v>323</v>
       </c>
@@ -36093,7 +36257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A416" s="14" t="s">
         <v>323</v>
       </c>
@@ -36161,7 +36325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A417" s="19" t="s">
         <v>323</v>
       </c>
@@ -36229,7 +36393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A418" s="14" t="s">
         <v>323</v>
       </c>
@@ -36297,7 +36461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A419" s="19" t="s">
         <v>323</v>
       </c>
@@ -36365,7 +36529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A420" s="14" t="s">
         <v>323</v>
       </c>
@@ -36433,7 +36597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A421" s="19" t="s">
         <v>323</v>
       </c>
@@ -36501,7 +36665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A422" s="14" t="s">
         <v>322</v>
       </c>
@@ -36569,7 +36733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A423" s="19" t="s">
         <v>322</v>
       </c>
@@ -36637,7 +36801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A424" s="19" t="s">
         <v>322</v>
       </c>
@@ -36705,7 +36869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A425" s="14" t="s">
         <v>322</v>
       </c>
@@ -36773,7 +36937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A426" s="19" t="s">
         <v>322</v>
       </c>
@@ -36841,7 +37005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A427" s="19" t="s">
         <v>322</v>
       </c>
@@ -36909,7 +37073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A428" s="19" t="s">
         <v>322</v>
       </c>
@@ -36977,7 +37141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A429" s="19" t="s">
         <v>322</v>
       </c>
@@ -37045,7 +37209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A430" s="14" t="s">
         <v>322</v>
       </c>
@@ -37113,7 +37277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A431" s="19" t="s">
         <v>322</v>
       </c>
@@ -37181,7 +37345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A432" s="14" t="s">
         <v>322</v>
       </c>
@@ -37249,7 +37413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A433" s="14" t="s">
         <v>322</v>
       </c>
@@ -37317,7 +37481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A434" s="19" t="s">
         <v>322</v>
       </c>
@@ -37385,7 +37549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A435" s="14" t="s">
         <v>322</v>
       </c>
@@ -37453,7 +37617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A436" s="19" t="s">
         <v>322</v>
       </c>
@@ -37521,7 +37685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A437" s="14" t="s">
         <v>321</v>
       </c>
@@ -37589,7 +37753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A438" s="19" t="s">
         <v>321</v>
       </c>
@@ -37657,7 +37821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A439" s="19" t="s">
         <v>321</v>
       </c>
@@ -37725,7 +37889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A440" s="14" t="s">
         <v>321</v>
       </c>
@@ -37793,7 +37957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A441" s="19" t="s">
         <v>321</v>
       </c>
@@ -37861,7 +38025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A442" s="14" t="s">
         <v>321</v>
       </c>
@@ -37929,7 +38093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A443" s="19" t="s">
         <v>321</v>
       </c>
@@ -37997,7 +38161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A444" s="14" t="s">
         <v>321</v>
       </c>
@@ -38065,7 +38229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A445" s="19" t="s">
         <v>321</v>
       </c>
@@ -38133,7 +38297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="446" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A446" s="14" t="s">
         <v>321</v>
       </c>
@@ -38201,7 +38365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A447" s="14" t="s">
         <v>321</v>
       </c>
@@ -38269,7 +38433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A448" s="19" t="s">
         <v>321</v>
       </c>
@@ -38337,7 +38501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A449" s="14" t="s">
         <v>321</v>
       </c>
@@ -38405,7 +38569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A450" s="19" t="s">
         <v>321</v>
       </c>
@@ -38473,7 +38637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A451" s="14" t="s">
         <v>321</v>
       </c>
@@ -38541,7 +38705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A452" s="19" t="s">
         <v>320</v>
       </c>
@@ -38609,7 +38773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A453" s="14" t="s">
         <v>320</v>
       </c>
@@ -38677,7 +38841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A454" s="14" t="s">
         <v>320</v>
       </c>
@@ -38745,7 +38909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A455" s="19" t="s">
         <v>320</v>
       </c>
@@ -38813,7 +38977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A456" s="14" t="s">
         <v>320</v>
       </c>
@@ -38881,7 +39045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A457" s="19" t="s">
         <v>320</v>
       </c>
@@ -38949,7 +39113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A458" s="14" t="s">
         <v>320</v>
       </c>
@@ -39017,7 +39181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A459" s="19" t="s">
         <v>320</v>
       </c>
@@ -39085,7 +39249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A460" s="14" t="s">
         <v>320</v>
       </c>
@@ -39153,7 +39317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A461" s="19" t="s">
         <v>320</v>
       </c>
@@ -39221,7 +39385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A462" s="14" t="s">
         <v>320</v>
       </c>
@@ -39289,7 +39453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A463" s="14" t="s">
         <v>320</v>
       </c>
@@ -39357,7 +39521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A464" s="19" t="s">
         <v>320</v>
       </c>
@@ -39425,7 +39589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A465" s="14" t="s">
         <v>319</v>
       </c>
@@ -39493,7 +39657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="466" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A466" s="19" t="s">
         <v>319</v>
       </c>
@@ -39561,7 +39725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A467" s="14" t="s">
         <v>319</v>
       </c>
@@ -39629,7 +39793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A468" s="19" t="s">
         <v>319</v>
       </c>
@@ -39697,7 +39861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A469" s="14" t="s">
         <v>319</v>
       </c>
@@ -39765,7 +39929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A470" s="19" t="s">
         <v>319</v>
       </c>
@@ -39833,7 +39997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A471" s="14" t="s">
         <v>319</v>
       </c>
@@ -39901,7 +40065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A472" s="14" t="s">
         <v>319</v>
       </c>
@@ -39969,7 +40133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="473" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A473" s="19" t="s">
         <v>319</v>
       </c>
@@ -40037,7 +40201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A474" s="14" t="s">
         <v>319</v>
       </c>
@@ -40105,7 +40269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A475" s="19" t="s">
         <v>319</v>
       </c>
@@ -40173,7 +40337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A476" s="19" t="s">
         <v>319</v>
       </c>
@@ -40241,7 +40405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A477" s="19" t="s">
         <v>319</v>
       </c>
@@ -40309,7 +40473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A478" s="14" t="s">
         <v>319</v>
       </c>
@@ -40377,7 +40541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A479" s="19" t="s">
         <v>319</v>
       </c>
@@ -40445,7 +40609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A480" s="19" t="s">
         <v>318</v>
       </c>
@@ -40513,7 +40677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A481" s="14" t="s">
         <v>318</v>
       </c>
@@ -40581,7 +40745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="482" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A482" s="19" t="s">
         <v>318</v>
       </c>
@@ -40649,7 +40813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A483" s="19" t="s">
         <v>318</v>
       </c>
@@ -40717,7 +40881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A484" s="14" t="s">
         <v>318</v>
       </c>
@@ -40785,7 +40949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A485" s="19" t="s">
         <v>318</v>
       </c>
@@ -40853,7 +41017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A486" s="14" t="s">
         <v>318</v>
       </c>
@@ -40921,7 +41085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A487" s="19" t="s">
         <v>318</v>
       </c>
@@ -40989,7 +41153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A488" s="14" t="s">
         <v>318</v>
       </c>
@@ -41057,7 +41221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A489" s="19" t="s">
         <v>318</v>
       </c>
@@ -41125,7 +41289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A490" s="14" t="s">
         <v>318</v>
       </c>
@@ -41193,7 +41357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A491" s="14" t="s">
         <v>318</v>
       </c>
@@ -41261,7 +41425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A492" s="19" t="s">
         <v>318</v>
       </c>
@@ -41329,7 +41493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A493" s="19" t="s">
         <v>318</v>
       </c>
@@ -41397,7 +41561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A494" s="14" t="s">
         <v>318</v>
       </c>
@@ -41484,8 +41648,8 @@
       <c r="F495" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G495" s="20" t="s">
-        <v>19</v>
+      <c r="G495" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H495" s="20" t="s">
         <v>311</v>
@@ -41552,8 +41716,8 @@
       <c r="F496" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G496" s="20" t="s">
-        <v>19</v>
+      <c r="G496" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H496" s="20" t="s">
         <v>311</v>
@@ -41621,7 +41785,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="G497" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H497" s="15" t="s">
         <v>311</v>
@@ -41688,8 +41852,8 @@
       <c r="F498" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G498" s="20" t="s">
-        <v>19</v>
+      <c r="G498" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H498" s="20" t="s">
         <v>311</v>
@@ -41756,8 +41920,8 @@
       <c r="F499" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G499" s="20" t="s">
-        <v>19</v>
+      <c r="G499" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H499" s="20" t="s">
         <v>311</v>
@@ -41825,7 +41989,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="G500" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H500" s="15" t="s">
         <v>311</v>
@@ -41893,7 +42057,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="G501" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H501" s="15" t="s">
         <v>311</v>
@@ -41960,8 +42124,8 @@
       <c r="F502" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G502" s="20" t="s">
-        <v>19</v>
+      <c r="G502" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H502" s="20" t="s">
         <v>311</v>
@@ -42028,8 +42192,8 @@
       <c r="F503" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G503" s="20" t="s">
-        <v>19</v>
+      <c r="G503" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H503" s="20" t="s">
         <v>311</v>
@@ -42096,8 +42260,8 @@
       <c r="F504" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G504" s="20" t="s">
-        <v>19</v>
+      <c r="G504" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H504" s="20" t="s">
         <v>311</v>
@@ -42164,8 +42328,8 @@
       <c r="F505" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G505" s="20" t="s">
-        <v>19</v>
+      <c r="G505" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H505" s="20" t="s">
         <v>311</v>
@@ -42232,8 +42396,8 @@
       <c r="F506" s="22">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G506" s="20" t="s">
-        <v>19</v>
+      <c r="G506" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="H506" s="20" t="s">
         <v>311</v>
@@ -42281,21 +42445,1000 @@
         <v>2</v>
       </c>
     </row>
+    <row r="507" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A507" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B507" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C507" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D507" s="24">
+        <v>8</v>
+      </c>
+      <c r="E507" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F507" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G507" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H507" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I507" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J507" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K507" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L507" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M507" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N507" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O507" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="P507" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q507" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R507 * 2) + (playerGameStats!$S507 * 3) + (playerGameStats!$T507)</f>
+        <v>0</v>
+      </c>
+      <c r="R507" s="24">
+        <v>0</v>
+      </c>
+      <c r="S507" s="24">
+        <v>0</v>
+      </c>
+      <c r="T507" s="24">
+        <v>0</v>
+      </c>
+      <c r="U507" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A508" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B508" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C508" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D508" s="24">
+        <v>8</v>
+      </c>
+      <c r="E508" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F508" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G508" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H508" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I508" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J508" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K508" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L508" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M508" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N508" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O508" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="P508" s="24">
+        <v>2</v>
+      </c>
+      <c r="Q508" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R508 * 2) + (playerGameStats!$S508 * 3) + (playerGameStats!$T508)</f>
+        <v>9</v>
+      </c>
+      <c r="R508" s="24">
+        <v>2</v>
+      </c>
+      <c r="S508" s="24">
+        <v>1</v>
+      </c>
+      <c r="T508" s="24">
+        <v>2</v>
+      </c>
+      <c r="U508" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="509" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A509" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B509" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C509" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D509" s="24">
+        <v>8</v>
+      </c>
+      <c r="E509" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F509" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G509" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H509" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I509" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J509" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K509" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L509" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M509" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N509" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O509" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="P509" s="24">
+        <v>3</v>
+      </c>
+      <c r="Q509" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R509 * 2) + (playerGameStats!$S509 * 3) + (playerGameStats!$T509)</f>
+        <v>8</v>
+      </c>
+      <c r="R509" s="24">
+        <v>0</v>
+      </c>
+      <c r="S509" s="24">
+        <v>2</v>
+      </c>
+      <c r="T509" s="24">
+        <v>2</v>
+      </c>
+      <c r="U509" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="510" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A510" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B510" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C510" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D510" s="24">
+        <v>8</v>
+      </c>
+      <c r="E510" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F510" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G510" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I510" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J510" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K510" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L510" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M510" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N510" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O510" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="P510" s="24">
+        <v>7</v>
+      </c>
+      <c r="Q510" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R510 * 2) + (playerGameStats!$S510 * 3) + (playerGameStats!$T510)</f>
+        <v>3</v>
+      </c>
+      <c r="R510" s="24">
+        <v>0</v>
+      </c>
+      <c r="S510" s="24">
+        <v>1</v>
+      </c>
+      <c r="T510" s="24">
+        <v>0</v>
+      </c>
+      <c r="U510" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A511" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B511" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C511" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D511" s="24">
+        <v>8</v>
+      </c>
+      <c r="E511" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F511" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G511" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H511" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I511" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J511" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K511" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L511" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M511" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N511" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O511" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="P511" s="24">
+        <v>9</v>
+      </c>
+      <c r="Q511" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R511 * 2) + (playerGameStats!$S511 * 3) + (playerGameStats!$T511)</f>
+        <v>3</v>
+      </c>
+      <c r="R511" s="24">
+        <v>1</v>
+      </c>
+      <c r="S511" s="24">
+        <v>0</v>
+      </c>
+      <c r="T511" s="24">
+        <v>1</v>
+      </c>
+      <c r="U511" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="512" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A512" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B512" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C512" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D512" s="24">
+        <v>8</v>
+      </c>
+      <c r="E512" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F512" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G512" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H512" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I512" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J512" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K512" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L512" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M512" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N512" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O512" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="P512" s="24">
+        <v>14</v>
+      </c>
+      <c r="Q512" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R512 * 2) + (playerGameStats!$S512 * 3) + (playerGameStats!$T512)</f>
+        <v>10</v>
+      </c>
+      <c r="R512" s="24">
+        <v>3</v>
+      </c>
+      <c r="S512" s="24">
+        <v>0</v>
+      </c>
+      <c r="T512" s="24">
+        <v>4</v>
+      </c>
+      <c r="U512" s="24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A513" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B513" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C513" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D513" s="24">
+        <v>8</v>
+      </c>
+      <c r="E513" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F513" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G513" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H513" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I513" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J513" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K513" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L513" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M513" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N513" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O513" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="P513" s="24">
+        <v>43</v>
+      </c>
+      <c r="Q513" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R513 * 2) + (playerGameStats!$S513 * 3) + (playerGameStats!$T513)</f>
+        <v>0</v>
+      </c>
+      <c r="R513" s="24">
+        <v>0</v>
+      </c>
+      <c r="S513" s="24">
+        <v>0</v>
+      </c>
+      <c r="T513" s="24">
+        <v>0</v>
+      </c>
+      <c r="U513" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A514" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B514" s="24">
+        <v>2026</v>
+      </c>
+      <c r="C514" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D514" s="24">
+        <v>8</v>
+      </c>
+      <c r="E514" s="24">
+        <v>46175</v>
+      </c>
+      <c r="F514" s="24">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G514" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H514" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="I514" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="J514" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K514" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L514" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="M514" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="N514" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O514" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="P514" s="24">
+        <v>53</v>
+      </c>
+      <c r="Q514" s="24">
+        <f xml:space="preserve"> (playerGameStats!$R514 * 2) + (playerGameStats!$S514 * 3) + (playerGameStats!$T514)</f>
+        <v>18</v>
+      </c>
+      <c r="R514" s="24">
+        <v>9</v>
+      </c>
+      <c r="S514" s="24">
+        <v>0</v>
+      </c>
+      <c r="T514" s="24">
+        <v>0</v>
+      </c>
+      <c r="U514" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A515" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B515" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C515" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D515" s="25">
+        <v>8</v>
+      </c>
+      <c r="E515" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F515" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G515" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H515" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I515" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J515" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K515" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L515" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M515" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N515" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O515" s="29" t="s">
+        <v>522</v>
+      </c>
+      <c r="P515" s="29">
+        <v>2</v>
+      </c>
+      <c r="Q515" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R515 * 2) + (playerGameStats!$S515 * 3) + (playerGameStats!$T515)</f>
+        <v>3</v>
+      </c>
+      <c r="R515" s="25">
+        <v>0</v>
+      </c>
+      <c r="S515" s="25">
+        <v>1</v>
+      </c>
+      <c r="T515" s="25">
+        <v>0</v>
+      </c>
+      <c r="U515" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A516" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B516" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C516" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D516" s="25">
+        <v>8</v>
+      </c>
+      <c r="E516" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F516" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G516" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H516" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I516" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J516" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K516" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L516" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M516" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N516" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O516" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="P516" s="29">
+        <v>3</v>
+      </c>
+      <c r="Q516" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R516 * 2) + (playerGameStats!$S516 * 3) + (playerGameStats!$T516)</f>
+        <v>23</v>
+      </c>
+      <c r="R516" s="25">
+        <v>4</v>
+      </c>
+      <c r="S516" s="25">
+        <v>4</v>
+      </c>
+      <c r="T516" s="25">
+        <v>3</v>
+      </c>
+      <c r="U516" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="517" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A517" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B517" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C517" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D517" s="25">
+        <v>8</v>
+      </c>
+      <c r="E517" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F517" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G517" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H517" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I517" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J517" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K517" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L517" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M517" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N517" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O517" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="P517" s="29">
+        <v>5</v>
+      </c>
+      <c r="Q517" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R517 * 2) + (playerGameStats!$S517 * 3) + (playerGameStats!$T517)</f>
+        <v>6</v>
+      </c>
+      <c r="R517" s="25">
+        <v>0</v>
+      </c>
+      <c r="S517" s="25">
+        <v>2</v>
+      </c>
+      <c r="T517" s="25">
+        <v>0</v>
+      </c>
+      <c r="U517" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A518" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B518" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C518" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D518" s="25">
+        <v>8</v>
+      </c>
+      <c r="E518" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F518" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G518" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H518" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I518" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J518" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K518" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L518" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M518" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N518" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O518" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="P518" s="26">
+        <v>8</v>
+      </c>
+      <c r="Q518" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R518 * 2) + (playerGameStats!$S518 * 3) + (playerGameStats!$T518)</f>
+        <v>12</v>
+      </c>
+      <c r="R518" s="25">
+        <v>3</v>
+      </c>
+      <c r="S518" s="25">
+        <v>2</v>
+      </c>
+      <c r="T518" s="25">
+        <v>0</v>
+      </c>
+      <c r="U518" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A519" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B519" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C519" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D519" s="25">
+        <v>8</v>
+      </c>
+      <c r="E519" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F519" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G519" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H519" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I519" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J519" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K519" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L519" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M519" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N519" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O519" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="P519" s="26">
+        <v>14</v>
+      </c>
+      <c r="Q519" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R519 * 2) + (playerGameStats!$S519 * 3) + (playerGameStats!$T519)</f>
+        <v>6</v>
+      </c>
+      <c r="R519" s="25">
+        <v>0</v>
+      </c>
+      <c r="S519" s="25">
+        <v>2</v>
+      </c>
+      <c r="T519" s="25">
+        <v>0</v>
+      </c>
+      <c r="U519" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A520" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B520" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C520" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D520" s="25">
+        <v>8</v>
+      </c>
+      <c r="E520" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F520" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G520" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H520" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I520" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J520" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K520" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L520" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M520" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N520" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O520" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="P520" s="26">
+        <v>21</v>
+      </c>
+      <c r="Q520" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R520 * 2) + (playerGameStats!$S520 * 3) + (playerGameStats!$T520)</f>
+        <v>0</v>
+      </c>
+      <c r="R520" s="25">
+        <v>0</v>
+      </c>
+      <c r="S520" s="25">
+        <v>0</v>
+      </c>
+      <c r="T520" s="25">
+        <v>0</v>
+      </c>
+      <c r="U520" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A521" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="B521" s="25">
+        <v>2026</v>
+      </c>
+      <c r="C521" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D521" s="25">
+        <v>8</v>
+      </c>
+      <c r="E521" s="27">
+        <v>46175</v>
+      </c>
+      <c r="F521" s="28">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G521" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H521" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="I521" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="J521" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K521" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="L521" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="M521" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="N521" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O521" s="26" t="s">
+        <v>526</v>
+      </c>
+      <c r="P521" s="26">
+        <v>30</v>
+      </c>
+      <c r="Q521" s="29">
+        <f xml:space="preserve"> (playerGameStats!$R521 * 2) + (playerGameStats!$S521 * 3) + (playerGameStats!$T521)</f>
+        <v>2</v>
+      </c>
+      <c r="R521" s="25">
+        <v>1</v>
+      </c>
+      <c r="S521" s="25">
+        <v>0</v>
+      </c>
+      <c r="T521" s="25">
+        <v>0</v>
+      </c>
+      <c r="U521" s="30">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U506" xr:uid="{614AF34C-B63C-4CF6-8513-43F58983B75E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026-w7-g06"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="7"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U506" xr:uid="{614AF34C-B63C-4CF6-8513-43F58983B75E}"/>
   <dataValidations count="1">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid stat value" error="Enter a whole number 0 or greater. Delete the row if this player did not play." sqref="Q2:U506" xr:uid="{00000000-0002-0000-0900-000000000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid stat value" error="Enter a whole number 0 or greater. Delete the row if this player did not play." sqref="Q2:U506 Q507:Q521" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -42307,7 +43450,7 @@
           <x14:formula1>
             <xm:f>players!$A$2:$A$84</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
+          <xm:sqref>N2:N506 N522:N1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
